--- a/practical-everyday-english/export/PRACTICAL_EVERYDAY_ENGLISH_MASTER.xlsx
+++ b/practical-everyday-english/export/PRACTICAL_EVERYDAY_ENGLISH_MASTER.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DIALOGUE_LINES" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIALOGUE_LINES" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6593,6 +6593,5226 @@
         <v>1</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SIT-011</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Booking a Taxi by Phone</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Đặt taxi qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Hello, I'd like to book a taxi, please.</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Chào em, anh muốn đặt một chuyến taxi.</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SIT-011</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Booking a Taxi by Phone</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Đặt taxi qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Of course. Can I take your name, please?</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Dạ được. Anh cho em xin tên được không?</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SIT-011</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Booking a Taxi by Phone</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Đặt taxi qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Yes, it's Ben.</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Được, tên anh là Ben.</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SIT-011</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Booking a Taxi by Phone</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Đặt taxi qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>4</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Sorry, could you spell that for me?</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Xin lỗi anh, anh đánh vần giúp em được không?</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SIT-011</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Booking a Taxi by Phone</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Đặt taxi qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>5</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Sure. B-E-N.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Được. B-E-N.</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SIT-011</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Booking a Taxi by Phone</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Đặt taxi qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>6</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>B-E-N, Ben. Got it. And where are you now?</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>B-E-N, Ben. Em ghi rồi. Anh đang ở đâu ạ?</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SIT-011</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Booking a Taxi by Phone</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Đặt taxi qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>7</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>I'm at 12 Green Street.</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Anh đang ở số 12 đường Green.</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SIT-011</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Booking a Taxi by Phone</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Đặt taxi qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>8</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Great. A taxi will be there in ten minutes.</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Được rồi. Xe sẽ đến trong mười phút nữa.</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SIT-011</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Booking a Taxi by Phone</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Đặt taxi qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>9</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Thank you very much.</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Anh cảm ơn em nhiều.</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SIT-011</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Booking a Taxi by Phone</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Đặt taxi qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>10</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>You're welcome. Have a good trip!</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Không có gì. Chúc anh đi đường vui vẻ!</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SIT-012</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Giving a Name for a Coffee Order</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Cho tên để gọi cà phê</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Hi, can I get a latte, please?</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Chào em, cho chị một ly latte nha.</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SIT-012</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Giving a Name for a Coffee Order</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Cho tên để gọi cà phê</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>2</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Sure. Can I have a name for the order?</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Dạ được. Chị cho em xin tên để gọi được không?</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SIT-012</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Giving a Name for a Coffee Order</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Cho tên để gọi cà phê</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>3</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>It's Mia.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Tên chị là Mia.</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SIT-012</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Giving a Name for a Coffee Order</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Cho tên để gọi cà phê</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>4</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Sorry, is that M-I-A?</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Xin lỗi chị, có phải là M-I-A không ạ?</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SIT-012</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Giving a Name for a Coffee Order</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Cho tên để gọi cà phê</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>5</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Yes, that's right, M-I-A.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Đúng rồi, M-I-A.</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SIT-012</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Giving a Name for a Coffee Order</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Cho tên để gọi cà phê</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>6</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Perfect, thank you. That'll be three fifty.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Vâng, em cảm ơn chị. Của chị là ba đô năm mươi.</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SIT-012</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Giving a Name for a Coffee Order</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Cho tên để gọi cà phê</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>7</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Here you go.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Đây nha em.</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SIT-012</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Giving a Name for a Coffee Order</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Cho tên để gọi cà phê</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>8</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Thanks. It'll be ready in a few minutes, Mia.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Em cảm ơn chị. Cà phê sẽ xong sau vài phút nữa, Mia nhé.</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SIT-012</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Giving a Name for a Coffee Order</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Cho tên để gọi cà phê</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>9</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>No problem, I'll wait over there.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Không sao, chị sẽ ngồi đợi ở đằng kia.</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SIT-013</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Exchanging Names in a Voice Chat</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Trao đổi tên trong cuộc gọi trực tuyến</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Hi, can you hear me okay?</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Chào bạn, bạn nghe mình rõ không?</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SIT-013</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Exchanging Names in a Voice Chat</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Trao đổi tên trong cuộc gọi trực tuyến</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>2</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Yes, I can hear you well. I'm Tom.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Có, mình nghe rõ. Mình là Tom.</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SIT-013</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Exchanging Names in a Voice Chat</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Trao đổi tên trong cuộc gọi trực tuyến</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>3</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Nice to meet you, Tom. Let me save your name. How do you spell it?</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Rất vui được gặp bạn, Tom. Để mình lưu tên bạn. Bạn đánh vần thế nào?</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SIT-013</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Exchanging Names in a Voice Chat</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Trao đổi tên trong cuộc gọi trực tuyến</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>4</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>It's T-O-M. Just four letters.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Là T-O-M. Chỉ bốn chữ thôi.</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SIT-013</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Exchanging Names in a Voice Chat</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Trao đổi tên trong cuộc gọi trực tuyến</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>5</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>T-O-M, easy. And I'm Anna.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>T-O-M, dễ nhớ. Còn mình là Anna.</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SIT-013</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Exchanging Names in a Voice Chat</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Trao đổi tên trong cuộc gọi trực tuyến</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>6</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Sorry, is that Anna with one N or two?</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Xin lỗi, Anna là một chữ N hay hai chữ N vậy?</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SIT-013</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Exchanging Names in a Voice Chat</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Trao đổi tên trong cuộc gọi trực tuyến</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>7</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Two Ns. A-N-N-A.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Hai chữ N. A-N-N-A.</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SIT-013</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Exchanging Names in a Voice Chat</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Trao đổi tên trong cuộc gọi trực tuyến</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>8</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Got it, Anna. Thanks for practising with me today.</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Mình ghi rồi, Anna. Cảm ơn bạn đã luyện tập cùng mình hôm nay.</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SIT-013</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Exchanging Names in a Voice Chat</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Trao đổi tên trong cuộc gọi trực tuyến</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>9</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>You're welcome. See you next time!</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Không có gì. Hẹn gặp lại lần sau nha!</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SIT-014</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Joining the Local Library</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Đăng ký thẻ thư viện</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Hi, I'd like to get a library card, please.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Chào anh, em muốn làm một thẻ thư viện.</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SIT-014</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Joining the Local Library</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Đăng ký thẻ thư viện</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>2</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Sure. What's your first name?</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Được. Tên của em là gì?</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SIT-014</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Joining the Local Library</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Đăng ký thẻ thư viện</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>3</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>It's Lily.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Tên em là Lily.</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SIT-014</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Joining the Local Library</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Đăng ký thẻ thư viện</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>4</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Lily... is that L-I-L-Y?</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Lily... có phải là L-I-L-Y không?</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SIT-014</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Joining the Local Library</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Đăng ký thẻ thư viện</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>5</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Yes, exactly. L-I-L-Y.</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Đúng rồi ạ. L-I-L-Y.</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SIT-014</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Joining the Local Library</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Đăng ký thẻ thư viện</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>6</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Thanks. And could I see some ID, please?</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Em cảm ơn. Anh cho em xem giấy tờ tùy thân được không?</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SIT-014</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Joining the Local Library</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Đăng ký thẻ thư viện</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>7</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Yes, here's my student card.</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Được, đây là thẻ học sinh của em.</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SIT-014</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Joining the Local Library</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Đăng ký thẻ thư viện</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>8</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Perfect. Your card will be ready in five minutes.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Tốt rồi. Thẻ của em sẽ xong trong năm phút nữa.</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>SIT-014</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Joining the Local Library</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Đăng ký thẻ thư viện</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>9</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Great, thank you so much.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Tuyệt, em cảm ơn anh nhiều.</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SIT-015</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Booking a Vet Appointment for a Pet</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Đặt hẹn khám thú y cho thú cưng</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Hello, I'd like to book a check-up for my pets, please.</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Chào chị, tôi muốn đặt hẹn khám sức khỏe cho thú cưng của tôi.</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SIT-015</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Booking a Vet Appointment for a Pet</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Đặt hẹn khám thú y cho thú cưng</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Of course. What kind of pets do you have?</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Dạ được. Anh có nuôi những loại thú cưng nào ạ?</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SIT-015</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Booking a Vet Appointment for a Pet</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Đặt hẹn khám thú y cho thú cưng</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>3</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>I have a cat and a dog.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Tôi có một con mèo và một con chó.</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>SIT-015</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Booking a Vet Appointment for a Pet</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Đặt hẹn khám thú y cho thú cưng</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>4</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Lovely. Could I have their names, please?</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Dễ thương quá. Anh cho tôi xin tên của hai bé được không?</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>SIT-015</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Booking a Vet Appointment for a Pet</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Đặt hẹn khám thú y cho thú cưng</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>5</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Yes, the cat is Milo, M-I-L-O, and the dog is Rex, R-E-X.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Được, con mèo tên Milo, M-I-L-O, và con chó tên Rex, R-E-X.</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SIT-015</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Booking a Vet Appointment for a Pet</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Đặt hẹn khám thú y cho thú cưng</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>6</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Milo and Rex, thank you. Which day suits you best?</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Milo và Rex, tôi cảm ơn anh. Anh muốn đến ngày nào thì tiện?</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SIT-015</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Booking a Vet Appointment for a Pet</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Đặt hẹn khám thú y cho thú cưng</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>7</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Saturday morning would be great, if possible.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Nếu được thì sáng thứ Bảy là tốt nhất.</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SIT-015</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Booking a Vet Appointment for a Pet</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Đặt hẹn khám thú y cho thú cưng</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>8</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>That works. See you and your pets on Saturday, then.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Được ạ. Vậy hẹn gặp anh và hai bé vào thứ Bảy nhé.</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>015</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SIT-015</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Booking a Vet Appointment for a Pet</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Đặt hẹn khám thú y cho thú cưng</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>9</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Thank you very much. See you then.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Cảm ơn chị nhiều. Hẹn gặp lại.</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SIT-016</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Fixing a Mistake in an Order Message</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Sửa lỗi trong tin nhắn đặt hàng</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Hi, I'd like to order a book and a ten, please.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Chào em, chị muốn đặt một cuốn sách và một cái ten.</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>SIT-016</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Fixing a Mistake in an Order Message</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Sửa lỗi trong tin nhắn đặt hàng</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>2</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Sorry, did you mean a pen? We don't have anything called a 'ten'.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Xin lỗi chị, chị có ý là cây bút không ạ? Bên em không có món nào tên là 'ten' cả.</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>SIT-016</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Fixing a Mistake in an Order Message</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Sửa lỗi trong tin nhắn đặt hàng</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>3</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Oh, sorry! Yes, a pen. P-E-N. My phone changed the word.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>À, xin lỗi! Đúng rồi, là cây bút. P-E-N. Điện thoại chị tự sửa chữ đó.</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SIT-016</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Fixing a Mistake in an Order Message</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Sửa lỗi trong tin nhắn đặt hàng</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>4</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>No worries, that happens a lot. So, one book and one pen?</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Không sao ạ, chuyện đó thường xảy ra lắm. Vậy là một cuốn sách và một cây bút phải không?</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SIT-016</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Fixing a Mistake in an Order Message</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Sửa lỗi trong tin nhắn đặt hàng</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>5</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Yes, that's right.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Đúng rồi đó.</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SIT-016</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Fixing a Mistake in an Order Message</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Sửa lỗi trong tin nhắn đặt hàng</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>6</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Great. Would you like the pen in blue or black?</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Được rồi. Chị muốn bút màu xanh hay màu đen?</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SIT-016</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Fixing a Mistake in an Order Message</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Sửa lỗi trong tin nhắn đặt hàng</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>7</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Black, please.</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Màu đen giúp em nha.</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SIT-016</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Fixing a Mistake in an Order Message</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Sửa lỗi trong tin nhắn đặt hàng</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>8</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Perfect. Your order will be ready this afternoon.</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Được rồi. Đơn hàng của chị sẽ xong vào chiều nay.</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SIT-016</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Fixing a Mistake in an Order Message</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Sửa lỗi trong tin nhắn đặt hàng</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>9</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Thanks for checking. I'll come by later.</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Cảm ơn em đã kiểm tra lại giúp chị. Chị sẽ ghé lấy sau.</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SIT-017</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Confirming a Colour on a Phone Order</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Xác nhận màu sắc khi đặt hàng qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Hi, I'd like to order a phone case, please.</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Chào anh, tôi muốn đặt một cái ốp điện thoại.</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SIT-017</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Confirming a Colour on a Phone Order</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Xác nhận màu sắc khi đặt hàng qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>2</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Sure. What colour would you like?</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Dạ được. Chị muốn màu gì ạ?</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SIT-017</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Confirming a Colour on a Phone Order</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Xác nhận màu sắc khi đặt hàng qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>3</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Red, please.</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Cho tôi màu đỏ.</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SIT-017</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Confirming a Colour on a Phone Order</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Xác nhận màu sắc khi đặt hàng qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>4</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Sorry, the line isn't very clear. Did you say red or blue?</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Xin lỗi chị, đường truyền không rõ lắm. Chị nói màu đỏ hay màu xanh vậy?</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SIT-017</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Confirming a Colour on a Phone Order</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Xác nhận màu sắc khi đặt hàng qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>5</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Red. R-E-D, like a tomato.</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Màu đỏ. R-E-D, giống màu cà chua đó.</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SIT-017</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Confirming a Colour on a Phone Order</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Xác nhận màu sắc khi đặt hàng qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>6</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Ah, red, got it. Sorry about that.</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>À, màu đỏ, em hiểu rồi. Xin lỗi chị nha.</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SIT-017</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Confirming a Colour on a Phone Order</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Xác nhận màu sắc khi đặt hàng qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>7</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>No problem at all.</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Không sao đâu.</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SIT-017</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Confirming a Colour on a Phone Order</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Xác nhận màu sắc khi đặt hàng qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>8</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>One red phone case. It'll arrive on Friday.</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Một ốp điện thoại màu đỏ. Hàng sẽ đến vào thứ Sáu.</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>017</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>SIT-017</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Confirming a Colour on a Phone Order</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Xác nhận màu sắc khi đặt hàng qua điện thoại</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>9</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Perfect, thank you.</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Tốt rồi, cảm ơn em.</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>SIT-018</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Asking How to Spell an Unfamiliar Word</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Hỏi cách đánh vần một từ chưa quen</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>You should try the new restaurant. The pho there is amazing.</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Bạn nên thử nhà hàng mới đó. Món phở ở đó ngon tuyệt.</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SIT-018</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Asking How to Spell an Unfamiliar Word</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Hỏi cách đánh vần một từ chưa quen</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>2</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>The what? Sorry, I didn't catch that word.</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Món gì cơ? Xin lỗi, mình chưa nghe rõ từ đó.</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>SIT-018</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Asking How to Spell an Unfamiliar Word</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Hỏi cách đánh vần một từ chưa quen</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>3</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Pho. It's a Vietnamese noodle soup.</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Phở. Đó là một món súp mì của Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>SIT-018</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Asking How to Spell an Unfamiliar Word</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Hỏi cách đánh vần một từ chưa quen</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>4</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Pho... how do you spell that?</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Phở... bạn viết từ đó thế nào?</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SIT-018</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Asking How to Spell an Unfamiliar Word</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Hỏi cách đánh vần một từ chưa quen</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>5</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>P-H-O.</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>P-H-O.</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SIT-018</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Asking How to Spell an Unfamiliar Word</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Hỏi cách đánh vần một từ chưa quen</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>6</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>P-H-O, okay. I'll look it up. It sounds delicious.</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>P-H-O, được rồi. Mình sẽ tìm hiểu thêm. Nghe có vẻ ngon đấy.</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SIT-018</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Asking How to Spell an Unfamiliar Word</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Hỏi cách đánh vần một từ chưa quen</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>7</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>It really is. We should go there together sometime.</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Ngon thật đó. Lúc nào mình đi cùng nhau nhé.</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SIT-018</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Asking How to Spell an Unfamiliar Word</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Hỏi cách đánh vần một từ chưa quen</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>8</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Definitely. Let's plan for this weekend.</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Chắc chắn rồi. Mình lên kế hoạch cho cuối tuần này đi.</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SIT-019</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Double-Checking an Email Address</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Kiểm tra lại địa chỉ email</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Can you check this email address for me before I send it?</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Chị xem lại giúp em địa chỉ email này trước khi em gửi được không?</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>SIT-019</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Double-Checking an Email Address</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Kiểm tra lại địa chỉ email</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>2</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Sure, let me have a look.</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Được, để chị xem thử.</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SIT-019</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Double-Checking an Email Address</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Kiểm tra lại địa chỉ email</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>3</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>It's h-a-n-a dot lee at mail dot com.</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Là h-a-n-a chấm lee, a-còng mail chấm com.</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SIT-019</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Double-Checking an Email Address</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Kiểm tra lại địa chỉ email</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>4</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Wait, is that hana with one N or two?</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Khoan, hana là một chữ N hay hai chữ N vậy?</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SIT-019</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Double-Checking an Email Address</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Kiểm tra lại địa chỉ email</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>5</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Just one N. H-A-N-A.</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Chỉ một chữ N thôi. H-A-N-A.</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SIT-019</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Double-Checking an Email Address</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Kiểm tra lại địa chỉ email</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>6</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Okay, one N. That looks correct now.</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Được rồi, một chữ N. Giờ thì đúng rồi.</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SIT-019</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Double-Checking an Email Address</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Kiểm tra lại địa chỉ email</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>7</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Great, thanks for catching that.</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Tốt, cảm ơn chị đã phát hiện ra chỗ sai đó.</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SIT-019</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Double-Checking an Email Address</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Kiểm tra lại địa chỉ email</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>8</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>No problem. It's always good to check twice.</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Không có gì. Kiểm tra lại lần nữa luôn tốt hơn.</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SIT-019</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Double-Checking an Email Address</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Kiểm tra lại địa chỉ email</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>9</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>You're right. I'll send it now.</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Chị nói đúng. Em gửi ngay đây.</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SIT-020</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Helping a Friend Practise Before a Test</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Giúp bạn ôn bài trước bài kiểm tra</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Are you ready for the spelling test?</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Bạn chuẩn bị xong cho bài kiểm tra đánh vần chưa?</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>SIT-020</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Helping a Friend Practise Before a Test</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Giúp bạn ôn bài trước bài kiểm tra</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>2</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Almost. Can you test me on a few words?</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Gần xong rồi. Bạn hỏi mình vài từ được không?</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>SIT-020</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Helping a Friend Practise Before a Test</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Giúp bạn ôn bài trước bài kiểm tra</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>3</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Sure. How do you spell 'friend'?</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Được. 'Friend' đánh vần thế nào?</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SIT-020</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Helping a Friend Practise Before a Test</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Giúp bạn ôn bài trước bài kiểm tra</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>4</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>F-R-I-E-N-D. Was that right?</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>F-R-I-E-N-D. Đúng không?</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SIT-020</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Helping a Friend Practise Before a Test</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Giúp bạn ôn bài trước bài kiểm tra</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>5</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Yes, perfect! Now, how about 'because'?</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Đúng, hoàn hảo! Giờ tới 'because' thì sao?</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SIT-020</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Helping a Friend Practise Before a Test</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Giúp bạn ôn bài trước bài kiểm tra</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>6</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>B-E-C-A-U-S-E. Hmm, I always mix that one up.</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>B-E-C-A-U-S-E. Ừm, từ đó mình hay bị lẫn.</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SIT-020</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Helping a Friend Practise Before a Test</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Giúp bạn ôn bài trước bài kiểm tra</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>7</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Don't worry, you got it right this time.</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Đừng lo, lần này bạn đúng rồi đó.</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SIT-020</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Helping a Friend Practise Before a Test</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Giúp bạn ôn bài trước bài kiểm tra</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>8</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Person B</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Thanks. I feel a bit more confident now.</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Cảm ơn bạn. Giờ mình thấy tự tin hơn một chút rồi.</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Checking and Confirming Information</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>SIT-020</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Helping a Friend Practise Before a Test</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Giúp bạn ôn bài trước bài kiểm tra</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Pre-A1.1</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>9</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Person A</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Good luck in the test!</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Chúc bạn may mắn trong bài kiểm tra!</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
